--- a/sampleprojects/CorporateTax/excel/states/TN_corp.xlsx
+++ b/sampleprojects/CorporateTax/excel/states/TN_corp.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="129">
   <si>
     <t>DT: Determine TN Filing Requirement</t>
   </si>
@@ -102,7 +102,7 @@
     <t>No nexus - no filing required</t>
   </si>
   <si>
-    <t>set apportionment.state_tax = 0.0; set result.tn_franchise_tax = 0.0; set result.tn_excise_tax = 0.0; set result.tn_total_tax = 0.0; set apportionment.state_refund_or_owed = apportionment.state_payments; add "No TN nexus - no filing requirement for franchise or excise tax. Any estimated payments would be refunded." to job.audit_trail;</t>
+    <t>set apportionment.state_tax = 0.0; set tn_result.franchise_tax = 0.0; set tn_result.excise_tax = 0.0; set tn_result.total_tax = 0.0; set apportionment.state_refund_or_owed = apportionment.state_payments; add "No TN nexus - no filing requirement for franchise or excise tax. Any estimated payments would be refunded." to job.audit_trail;</t>
   </si>
   <si>
     <t>DT: Calculate TN Income Adjustments</t>
@@ -126,7 +126,7 @@
     <t>Calculate TN state additions and subtractions</t>
   </si>
   <si>
-    <t>set apportionment.state_additions = 0.0; if revenue.federal_bond_interest != null then set apportionment.state_additions = apportionment.state_additions + revenue.federal_bond_interest; endif if result.section_199a_deduction != null then set apportionment.state_additions = apportionment.state_additions + result.section_199a_deduction; endif if result.state_income_taxes_paid != null then set apportionment.state_additions = apportionment.state_additions + result.state_income_taxes_paid; endif set apportionment.state_subtractions = 0.0; if revenue.tn_municipal_interest != null then set apportionment.state_subtractions = apportionment.state_subtractions + revenue.tn_municipal_interest; endif if revenue.qualified_subsidiary_dividends != null then set apportionment.state_subtractions = apportionment.state_subtractions + revenue.qualified_subsidiary_dividends; endif if result.tn_nol_deduction != null then set apportionment.state_subtractions = apportionment.state_subtractions + result.tn_nol_deduction; endif add "TN state-specific income adjustments to federal taxable income. Additions include: Interest on federal obligations (U.S. Treasury bonds, etc.), IRC § 199A qualified business income deduction addback, State franchise and excise taxes paid (not deductible). Subtractions include: Interest on TN state and local bonds, Dividends from 80%+ owned subsidiaries, TN NOL carryforward deduction. Reference: TN Code § 67-4-2006 (Definitions of net earnings), Form FAE 170 Instructions (Schedule J - Adjustments), TN Revenue Ruling 09-13 (IRC conformity)" to job.audit_trail;</t>
+    <t>set apportionment.state_additions = 0.0; if revenue.federal_bond_interest != null then set apportionment.state_additions = apportionment.state_additions + revenue.federal_bond_interest; endif if result.section_199a_deduction != null then set apportionment.state_additions = apportionment.state_additions + result.section_199a_deduction; endif if result.state_income_taxes_paid != null then set apportionment.state_additions = apportionment.state_additions + result.state_income_taxes_paid; endif set apportionment.state_subtractions = 0.0; if revenue.tn_municipal_interest != null then set apportionment.state_subtractions = apportionment.state_subtractions + revenue.tn_municipal_interest; endif if revenue.qualified_subsidiary_dividends != null then set apportionment.state_subtractions = apportionment.state_subtractions + revenue.qualified_subsidiary_dividends; endif if tn_result.nol_deduction != null then set apportionment.state_subtractions = apportionment.state_subtractions + tn_result.nol_deduction; endif add "TN state-specific income adjustments to federal taxable income. Additions include: Interest on federal obligations (U.S. Treasury bonds, etc.), IRC § 199A qualified business income deduction addback, State franchise and excise taxes paid (not deductible). Subtractions include: Interest on TN state and local bonds, Dividends from 80%+ owned subsidiaries, TN NOL carryforward deduction. Reference: TN Code § 67-4-2006 (Definitions of net earnings), Form FAE 170 Instructions (Schedule J - Adjustments), TN Revenue Ruling 09-13 (IRC conformity)" to job.audit_trail;</t>
   </si>
   <si>
     <t>No nexus - no TN state adjustments calculated</t>
@@ -153,25 +153,25 @@
     <t>Has positive net worth in TN</t>
   </si>
   <si>
-    <t>result.tn_net_worth &gt; 0</t>
+    <t>tn_result.net_worth &gt; 0</t>
   </si>
   <si>
     <t>Calculate franchise tax: 0.25% on net worth</t>
   </si>
   <si>
-    <t>set result.tn_franchise_tax = result.tn_net_worth * result.tn_franchise_tax_rate; add "TN franchise tax calculation: Net worth × 0.25%. Combined minimum tax (franchise + excise): $100. Reference: TN Code 67-4-2104" to job.audit_trail;</t>
+    <t>set tn_result.franchise_tax = tn_result.net_worth * tn_result.franchise_tax_rate; add "TN franchise tax calculation: Net worth × 0.25%. Combined minimum tax (franchise + excise): $100. Reference: TN Code 67-4-2104" to job.audit_trail;</t>
   </si>
   <si>
     <t>No net worth - franchise tax is zero</t>
   </si>
   <si>
-    <t>set result.tn_franchise_tax = 0.0; add "No net worth in TN - no franchise tax liability. Excise tax may still apply if there is net earnings." to job.audit_trail;</t>
+    <t>set tn_result.franchise_tax = 0.0; add "No net worth in TN - no franchise tax liability. Excise tax may still apply if there is net earnings." to job.audit_trail;</t>
   </si>
   <si>
     <t>No TN nexus - no franchise tax liability</t>
   </si>
   <si>
-    <t>set result.tn_franchise_tax = 0.0; add "No TN nexus - no franchise tax liability." to job.audit_trail;</t>
+    <t>set tn_result.franchise_tax = 0.0; add "No TN nexus - no franchise tax liability." to job.audit_trail;</t>
   </si>
   <si>
     <t>DT: Calculate TN Excise Tax</t>
@@ -198,19 +198,19 @@
     <t>Calculate excise tax: 6.5% on apportioned income</t>
   </si>
   <si>
-    <t>set result.tn_excise_tax = apportionment.state_taxable_income * apportionment.state_tax_rate; set result.tn_excise_tax = the maximum of (result.tn_excise_tax - apportionment.state_credits) and (0.0); set result.tn_total_tax = result.tn_franchise_tax + result.tn_excise_tax; set result.tn_total_tax = the maximum of (result.tn_minimum_tax) and (result.tn_total_tax); set apportionment.state_tax = result.tn_total_tax; set apportionment.state_refund_or_owed = apportionment.state_payments - apportionment.state_tax; add "TN franchise and excise tax calculated. Excise: 6.5% on net earnings. Franchise: 0.25% on net worth. Minimum $100. Reference: TN Code 67-4-2007, 67-4-2104" to job.audit_trail;</t>
+    <t>set tn_result.excise_tax = apportionment.state_taxable_income * tn_apportionment.state_tax_rate; set tn_result.excise_tax = the maximum of (tn_result.excise_tax - apportionment.state_credits) and (0.0); set tn_result.total_tax = tn_result.franchise_tax + tn_result.excise_tax; set tn_result.total_tax = the maximum of (tn_result.minimum_tax) and (tn_result.total_tax); set apportionment.state_tax = tn_result.total_tax; set apportionment.state_refund_or_owed = apportionment.state_payments - apportionment.state_tax; add "TN franchise and excise tax calculated. Excise: 6.5% on net earnings. Franchise: 0.25% on net worth. Minimum $100. Reference: TN Code 67-4-2007, 67-4-2104" to job.audit_trail;</t>
   </si>
   <si>
     <t>No net earnings - excise tax is zero</t>
   </si>
   <si>
-    <t>set result.tn_excise_tax = 0.0; set result.tn_total_tax = result.tn_franchise_tax; if result.tn_franchise_tax &gt; 0 then set result.tn_total_tax = the maximum of (result.tn_minimum_tax) and (result.tn_total_tax); endif set apportionment.state_tax = result.tn_total_tax; set apportionment.state_refund_or_owed = apportionment.state_payments - apportionment.state_tax; add "No TN net earnings - no excise tax. Franchise tax still applies if there is net worth. Minimum $100 if franchise tax owed." to job.audit_trail;</t>
+    <t>set tn_result.excise_tax = 0.0; set tn_result.total_tax = tn_result.franchise_tax; if tn_result.franchise_tax &gt; 0 then set tn_result.total_tax = the maximum of (tn_result.minimum_tax) and (tn_result.total_tax); endif set apportionment.state_tax = tn_result.total_tax; set apportionment.state_refund_or_owed = apportionment.state_payments - apportionment.state_tax; add "No TN net earnings - no excise tax. Franchise tax still applies if there is net worth. Minimum $100 if franchise tax owed." to job.audit_trail;</t>
   </si>
   <si>
     <t>No nexus - no excise tax or franchise tax liability</t>
   </si>
   <si>
-    <t>set result.tn_excise_tax = 0.0; set result.tn_total_tax = 0.0; set apportionment.state_tax = 0.0; set apportionment.state_refund_or_owed = apportionment.state_payments; add "No TN nexus - no excise tax or franchise tax liability. Any estimated payments are refunded." to job.audit_trail;</t>
+    <t>set tn_result.excise_tax = 0.0; set tn_result.total_tax = 0.0; set apportionment.state_tax = 0.0; set apportionment.state_refund_or_owed = apportionment.state_payments; add "No TN nexus - no excise tax or franchise tax liability. Any estimated payments are refunded." to job.audit_trail;</t>
   </si>
   <si>
     <t>DT: Calculate TN State Tax</t>
@@ -279,106 +279,82 @@
     <t>Reference</t>
   </si>
   <si>
-    <t>apportionment</t>
+    <t>tn_apportionment</t>
+  </si>
+  <si>
+    <t>(4 attributes)</t>
+  </si>
+  <si>
+    <t>apportionment_formula</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>single_sales</t>
+  </si>
+  <si>
+    <t>r</t>
+  </si>
+  <si>
+    <t>TN uses single-sales factor apportionment</t>
+  </si>
+  <si>
+    <t>economic_nexus_threshold</t>
+  </si>
+  <si>
+    <t>double</t>
+  </si>
+  <si>
+    <t>100000.0</t>
+  </si>
+  <si>
+    <t>TN economic nexus threshold: $100,000 gross receipts</t>
+  </si>
+  <si>
+    <t>state_tax_rate</t>
+  </si>
+  <si>
+    <t>0.0650</t>
+  </si>
+  <si>
+    <t>TN excise tax rate: 6.5% on net earnings (TN Code § 67-4-2007)</t>
+  </si>
+  <si>
+    <t>transaction_threshold</t>
+  </si>
+  <si>
+    <t>integer</t>
+  </si>
+  <si>
+    <t>200</t>
+  </si>
+  <si>
+    <t>TN economic nexus transaction threshold: 200 transactions</t>
+  </si>
+  <si>
+    <t>tn_result</t>
   </si>
   <si>
     <t>(8 attributes)</t>
   </si>
   <si>
-    <t>apportionment_formula</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>single_sales</t>
-  </si>
-  <si>
-    <t>r</t>
-  </si>
-  <si>
-    <t>TN uses single-sales factor apportionment</t>
-  </si>
-  <si>
-    <t>economic_nexus_threshold</t>
-  </si>
-  <si>
-    <t>double</t>
-  </si>
-  <si>
-    <t>100000.0</t>
-  </si>
-  <si>
-    <t>TN economic nexus threshold: $100,000 gross receipts</t>
-  </si>
-  <si>
-    <t>state_additions</t>
+    <t>excise_tax</t>
   </si>
   <si>
     <t>0.0</t>
   </si>
   <si>
-    <t>TN-specific additions to federal taxable income</t>
-  </si>
-  <si>
-    <t>state_code</t>
-  </si>
-  <si>
-    <t>TN</t>
-  </si>
-  <si>
-    <t>Tennessee - Two-letter state code</t>
-  </si>
-  <si>
-    <t>state_credits</t>
-  </si>
-  <si>
-    <t>TN tax credits: jobs, investment, research, headquarters, etc.</t>
-  </si>
-  <si>
-    <t>state_subtractions</t>
-  </si>
-  <si>
-    <t>TN-specific subtractions from federal taxable income</t>
-  </si>
-  <si>
-    <t>state_tax_rate</t>
-  </si>
-  <si>
-    <t>0.0650</t>
-  </si>
-  <si>
-    <t>TN excise tax rate: 6.5% on net earnings (TN Code § 67-4-2007)</t>
-  </si>
-  <si>
-    <t>transaction_threshold</t>
-  </si>
-  <si>
-    <t>integer</t>
-  </si>
-  <si>
-    <t>200</t>
-  </si>
-  <si>
-    <t>TN economic nexus transaction threshold: 200 transactions</t>
-  </si>
-  <si>
-    <t>result</t>
-  </si>
-  <si>
-    <t>tn_excise_tax</t>
-  </si>
-  <si>
     <t>TN excise tax calculated: apportioned_income × 0.065</t>
   </si>
   <si>
-    <t>tn_franchise_tax</t>
+    <t>franchise_tax</t>
   </si>
   <si>
     <t>TN franchise tax calculated: net_worth × 0.0025</t>
   </si>
   <si>
-    <t>tn_franchise_tax_rate</t>
+    <t>franchise_tax_rate</t>
   </si>
   <si>
     <t>0.0025</t>
@@ -387,7 +363,7 @@
     <t>TN franchise tax rate: 0.25% (TN Code § 67-4-2104)</t>
   </si>
   <si>
-    <t>tn_minimum_tax</t>
+    <t>minimum_tax</t>
   </si>
   <si>
     <t>100.0</t>
@@ -396,13 +372,13 @@
     <t>TN minimum combined tax: $100 (applies to both franchise + excise)</t>
   </si>
   <si>
-    <t>tn_net_worth</t>
+    <t>net_worth</t>
   </si>
   <si>
     <t>TN net worth: greater of (1) capital stock + surplus + undivided profits or (2) property owned/used in TN</t>
   </si>
   <si>
-    <t>tn_net_worth_method</t>
+    <t>net_worth_method</t>
   </si>
   <si>
     <t>greater_of_book_or_property</t>
@@ -411,25 +387,25 @@
     <t>TN net worth calculation method: greater_of_book_or_property</t>
   </si>
   <si>
-    <t>tn_nol_deduction</t>
+    <t>nol_deduction</t>
   </si>
   <si>
     <t>Declared from decision-table usage; referenced by TN but never declared (campaign #948 Phase 1)</t>
   </si>
   <si>
-    <t>tn_total_tax</t>
+    <t>total_tax</t>
   </si>
   <si>
     <t>TN total tax: franchise_tax + excise_tax</t>
   </si>
   <si>
-    <t>revenue</t>
+    <t>tn_revenue</t>
   </si>
   <si>
     <t>(1 attributes)</t>
   </si>
   <si>
-    <t>tn_municipal_interest</t>
+    <t>municipal_interest</t>
   </si>
 </sst>
 </file>
@@ -3843,14 +3819,14 @@
       <c r="B7" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="C7" s="10" t="s">
-        <v>89</v>
+      <c r="C7" s="11" t="s">
+        <v>101</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>8</v>
@@ -3859,7 +3835,7 @@
         <v>91</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I7" s="8" t="s">
         <v>8</v>
@@ -3878,194 +3854,194 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="H8" s="16" t="s">
+      <c r="A8" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="I8" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="L8" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="M8" s="7" t="s">
-        <v>8</v>
-      </c>
+      <c r="B8" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>8</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="D9" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G9" s="8" t="s">
+      <c r="D9" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G9" s="7" t="s">
         <v>91</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>106</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="J9" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="K9" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="L9" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="M9" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L9" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M9" s="7" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="8" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="D10" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="G10" s="7" t="s">
+      <c r="D10" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G10" s="8" t="s">
         <v>91</v>
       </c>
       <c r="H10" s="16" t="s">
-        <v>109</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="K10" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="L10" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="M10" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M10" s="8" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="7" t="s">
         <v>8</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E11" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="F11" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G11" s="8" t="s">
+      <c r="F11" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G11" s="7" t="s">
         <v>91</v>
       </c>
       <c r="H11" s="16" t="s">
         <v>113</v>
       </c>
-      <c r="I11" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="J11" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="K11" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="L11" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="M11" s="8" t="s">
+      <c r="I11" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J11" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L11" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M11" s="7" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
-      <c r="K12" s="6"/>
-      <c r="L12" s="6"/>
-      <c r="M12" s="6"/>
+      <c r="C12" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="H12" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M12" s="8" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="s">
         <v>8</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C13" s="11" t="s">
         <v>94</v>
@@ -4074,7 +4050,7 @@
         <v>8</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="F13" s="7" t="s">
         <v>8</v>
@@ -4083,7 +4059,7 @@
         <v>91</v>
       </c>
       <c r="H13" s="16" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="I13" s="7" t="s">
         <v>8</v>
@@ -4106,16 +4082,16 @@
         <v>8</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>94</v>
+        <v>119</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>89</v>
       </c>
       <c r="D14" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>98</v>
+        <v>120</v>
       </c>
       <c r="F14" s="8" t="s">
         <v>8</v>
@@ -4124,7 +4100,7 @@
         <v>91</v>
       </c>
       <c r="H14" s="16" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="I14" s="8" t="s">
         <v>8</v>
@@ -4147,7 +4123,7 @@
         <v>8</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C15" s="11" t="s">
         <v>94</v>
@@ -4156,7 +4132,7 @@
         <v>8</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="F15" s="7" t="s">
         <v>8</v>
@@ -4165,7 +4141,7 @@
         <v>91</v>
       </c>
       <c r="H15" s="16" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="I15" s="7" t="s">
         <v>8</v>
@@ -4188,7 +4164,7 @@
         <v>8</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C16" s="11" t="s">
         <v>94</v>
@@ -4197,7 +4173,7 @@
         <v>8</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="F16" s="8" t="s">
         <v>8</v>
@@ -4206,7 +4182,7 @@
         <v>91</v>
       </c>
       <c r="H16" s="16" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I16" s="8" t="s">
         <v>8</v>
@@ -4225,226 +4201,62 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="C17" s="11" t="s">
+      <c r="A17" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="6"/>
+      <c r="K17" s="6"/>
+      <c r="L17" s="6"/>
+      <c r="M17" s="6"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="C18" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="D17" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="G17" s="7" t="s">
+      <c r="D18" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G18" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="H17" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="I17" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="J17" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="K17" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="L17" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="M17" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="F18" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G18" s="8" t="s">
-        <v>91</v>
-      </c>
       <c r="H18" s="16" t="s">
-        <v>129</v>
-      </c>
-      <c r="I18" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="J18" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="K18" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="L18" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="M18" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B19" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="F19" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="G19" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="H19" s="16" t="s">
-        <v>131</v>
-      </c>
-      <c r="I19" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="J19" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="K19" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="L19" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="M19" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B20" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="F20" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G20" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="H20" s="16" t="s">
-        <v>133</v>
-      </c>
-      <c r="I20" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="J20" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="K20" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="L20" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="M20" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="6"/>
-      <c r="J21" s="6"/>
-      <c r="K21" s="6"/>
-      <c r="L21" s="6"/>
-      <c r="M21" s="6"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B22" s="9" t="s">
-        <v>136</v>
-      </c>
-      <c r="C22" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="F22" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="G22" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="H22" s="16" t="s">
-        <v>131</v>
-      </c>
-      <c r="I22" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="J22" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="K22" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="L22" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="M22" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="I18" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J18" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K18" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L18" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M18" s="7" t="s">
         <v>8</v>
       </c>
     </row>
